--- a/04_DESIGN_TABLES/DesignTable_2701.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2701.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,12 +635,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | no Brennan catalog row</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2701-LN-04-04-FG</t>
         </is>
       </c>
     </row>
@@ -2859,6 +2864,150 @@
       <c r="R37" t="inlineStr">
         <is>
           <t>2701-05-05-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2701-02-02-FG-LN</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2701-02-02-FG-LN</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5/16-24 (B (1) SAE 37) x 5/16-24 (B (2) SAE 37)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU 2701-LN-02-02-FG dropped by the 2026-09-23 crawl (adapters77 2026-10-16); -LN = the plain 2701-02-02-FG + a locknut (A10 Q-TRANSFER-LN yes 2026-10-18): every size = row 2701-02-02-FG (its own Brennan STEP, batch 15)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells 2701-LN-02-02-FG; copied from 2701-02-02-FG (A10: -LN modelled as the plain part, no locknut)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2701-LN-02-02-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2701-05-05-FG-LN</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2701-05-05-FG-LN</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1/2-20 (B (1) SAE 37) x 1/2-20 (B (2) SAE 37)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU 2701-LN-05-05-FG dropped by the 2026-09-23 crawl (adapters77 2026-10-16); -LN = the plain 2701-05-05-FG + a locknut (A10 Q-TRANSFER-LN yes 2026-10-18): every size = row 2701-05-05-FG (its own Brennan STEP, batch 15)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells 2701-LN-05-05-FG; copied from 2701-05-05-FG (A10: -LN modelled as the plain part, no locknut)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2701-LN-05-05-FG</t>
         </is>
       </c>
     </row>
